--- a/data/preliminaries/stellar/female/23-preliminary-r07-stellar-female.xlsx
+++ b/data/preliminaries/stellar/female/23-preliminary-r07-stellar-female.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>进入第5轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
